--- a/final_data_pipeline/output/312140longform.xlsx
+++ b/final_data_pipeline/output/312140longform.xlsx
@@ -822,7 +822,7 @@
         <v>81</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -911,7 +911,7 @@
         <v>81</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1000,7 +1000,7 @@
         <v>81</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1092,7 +1092,7 @@
         <v>81</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1187,7 +1187,7 @@
         <v>81</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1276,7 +1276,7 @@
         <v>81</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -2445,7 +2445,7 @@
         <v>81</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2534,7 +2534,7 @@
         <v>81</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2623,7 +2623,7 @@
         <v>81</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2712,7 +2712,7 @@
         <v>81</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -2804,7 +2804,7 @@
         <v>81</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -2899,7 +2899,7 @@
         <v>81</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -2991,7 +2991,7 @@
         <v>81</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB26">
         <v>8000</v>
@@ -3086,7 +3086,7 @@
         <v>81</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB27">
         <v>8000</v>
@@ -3175,7 +3175,7 @@
         <v>81</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB28">
         <v>8000</v>
@@ -3264,7 +3264,7 @@
         <v>81</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB29">
         <v>8000</v>
@@ -3353,7 +3353,7 @@
         <v>81</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB30">
         <v>8000</v>
@@ -3442,7 +3442,7 @@
         <v>81</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB31">
         <v>8000</v>
@@ -3531,7 +3531,7 @@
         <v>81</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB32">
         <v>8000</v>
@@ -3620,7 +3620,7 @@
         <v>81</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB33">
         <v>8000</v>
@@ -3709,7 +3709,7 @@
         <v>81</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB34">
         <v>8000</v>
@@ -3798,7 +3798,7 @@
         <v>81</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB35">
         <v>8000</v>
@@ -3890,7 +3890,7 @@
         <v>81</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB36">
         <v>8000</v>
@@ -3985,7 +3985,7 @@
         <v>81</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -4617,7 +4617,7 @@
         <v>81</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -4712,7 +4712,7 @@
         <v>81</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -4807,7 +4807,7 @@
         <v>81</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -4896,7 +4896,7 @@
         <v>81</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB47">
         <v>8000</v>
@@ -4985,7 +4985,7 @@
         <v>81</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB48">
         <v>8000</v>
@@ -5074,7 +5074,7 @@
         <v>81</v>
       </c>
       <c r="AA49">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB49">
         <v>8000</v>
@@ -5163,7 +5163,7 @@
         <v>81</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -5252,7 +5252,7 @@
         <v>81</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -5341,7 +5341,7 @@
         <v>81</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5430,7 +5430,7 @@
         <v>81</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5519,7 +5519,7 @@
         <v>81</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5608,7 +5608,7 @@
         <v>81</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5697,7 +5697,7 @@
         <v>81</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -5786,7 +5786,7 @@
         <v>81</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -5875,7 +5875,7 @@
         <v>81</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -5964,7 +5964,7 @@
         <v>81</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6053,7 +6053,7 @@
         <v>81</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -7231,7 +7231,7 @@
         <v>81</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -7323,7 +7323,7 @@
         <v>81</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -7421,7 +7421,7 @@
         <v>81</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7516,7 +7516,7 @@
         <v>81</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -7605,7 +7605,7 @@
         <v>81</v>
       </c>
       <c r="AA77">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB77">
         <v>8000</v>
@@ -7694,7 +7694,7 @@
         <v>81</v>
       </c>
       <c r="AA78">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB78">
         <v>8000</v>
@@ -7783,7 +7783,7 @@
         <v>81</v>
       </c>
       <c r="AA79">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB79">
         <v>8000</v>
@@ -7872,7 +7872,7 @@
         <v>81</v>
       </c>
       <c r="AA80">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB80">
         <v>8000</v>
@@ -7961,7 +7961,7 @@
         <v>81</v>
       </c>
       <c r="AA81">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB81">
         <v>8000</v>
@@ -8050,7 +8050,7 @@
         <v>81</v>
       </c>
       <c r="AA82">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB82">
         <v>8000</v>
@@ -8139,7 +8139,7 @@
         <v>81</v>
       </c>
       <c r="AA83">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB83">
         <v>8000</v>
@@ -8228,7 +8228,7 @@
         <v>81</v>
       </c>
       <c r="AA84">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB84">
         <v>8000</v>
@@ -8317,7 +8317,7 @@
         <v>81</v>
       </c>
       <c r="AA85">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB85">
         <v>8000</v>
@@ -8406,7 +8406,7 @@
         <v>81</v>
       </c>
       <c r="AA86">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB86">
         <v>8000</v>
@@ -8495,7 +8495,7 @@
         <v>81</v>
       </c>
       <c r="AA87">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB87">
         <v>8000</v>
@@ -8584,7 +8584,7 @@
         <v>81</v>
       </c>
       <c r="AA88">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB88">
         <v>8000</v>
@@ -8673,7 +8673,7 @@
         <v>81</v>
       </c>
       <c r="AA89">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB89">
         <v>8000</v>
@@ -8762,7 +8762,7 @@
         <v>81</v>
       </c>
       <c r="AA90">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB90">
         <v>8000</v>
@@ -8851,7 +8851,7 @@
         <v>81</v>
       </c>
       <c r="AA91">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB91">
         <v>8000</v>
@@ -8940,7 +8940,7 @@
         <v>81</v>
       </c>
       <c r="AA92">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB92">
         <v>8000</v>
@@ -9029,7 +9029,7 @@
         <v>81</v>
       </c>
       <c r="AA93">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB93">
         <v>8000</v>
@@ -9118,7 +9118,7 @@
         <v>81</v>
       </c>
       <c r="AA94">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB94">
         <v>8000</v>
@@ -9210,7 +9210,7 @@
         <v>81</v>
       </c>
       <c r="AA95">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB95">
         <v>8000</v>
@@ -9305,7 +9305,7 @@
         <v>81</v>
       </c>
       <c r="AA96">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB96">
         <v>8000</v>
@@ -9394,7 +9394,7 @@
         <v>81</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -9483,7 +9483,7 @@
         <v>81</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -9575,7 +9575,7 @@
         <v>81</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -9664,7 +9664,7 @@
         <v>81</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -9753,7 +9753,7 @@
         <v>81</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -9842,7 +9842,7 @@
         <v>81</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -9931,7 +9931,7 @@
         <v>81</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -10020,7 +10020,7 @@
         <v>81</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -10109,7 +10109,7 @@
         <v>81</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -10198,7 +10198,7 @@
         <v>81</v>
       </c>
       <c r="AA106">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB106">
         <v>8000</v>
@@ -10287,7 +10287,7 @@
         <v>81</v>
       </c>
       <c r="AA107">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB107">
         <v>8000</v>
@@ -10376,7 +10376,7 @@
         <v>81</v>
       </c>
       <c r="AA108">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB108">
         <v>8000</v>
@@ -10465,7 +10465,7 @@
         <v>81</v>
       </c>
       <c r="AA109">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB109">
         <v>8000</v>
@@ -10554,7 +10554,7 @@
         <v>81</v>
       </c>
       <c r="AA110">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB110">
         <v>8000</v>
@@ -10646,7 +10646,7 @@
         <v>81</v>
       </c>
       <c r="AA111">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB111">
         <v>8000</v>
@@ -10738,7 +10738,7 @@
         <v>81</v>
       </c>
       <c r="AA112">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB112">
         <v>8000</v>
@@ -10833,7 +10833,7 @@
         <v>81</v>
       </c>
       <c r="AA113">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB113">
         <v>8000</v>
@@ -10922,7 +10922,7 @@
         <v>81</v>
       </c>
       <c r="AA114">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AB114">
         <v>8000</v>
